--- a/word-lists/100-wordlist-Russian.xlsx
+++ b/word-lists/100-wordlist-Russian.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\KDrive\Project\Keyboard\keyboard heaven - in work\KeyDual Github readme\Claude word list docs and files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\KDrive\Project\Keyboard\keyboard heaven - in work\KeyDual Github readme\Wordlist 2026-04-20 files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C7F7383-75D4-42EA-BD6E-BA30F0E51531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E9C6497-93CC-4565-BAF3-ABA29DD62C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5649" yWindow="2049" windowWidth="24685" windowHeight="13054" xr2:uid="{DD057330-9A83-4595-B84E-FF85E1D36A31}"/>
+    <workbookView xWindow="5649" yWindow="2049" windowWidth="24685" windowHeight="13054" xr2:uid="{E45B48CC-2468-4143-B6C8-026F2869D2B5}"/>
   </bookViews>
   <sheets>
     <sheet name="100-wordlist-Russian" sheetId="1" r:id="rId1"/>
@@ -327,13 +327,13 @@
     <t>правительство</t>
   </si>
   <si>
-    <t>важный</t>
+    <t>возможность</t>
   </si>
   <si>
     <t>различный</t>
   </si>
   <si>
-    <t>данные</t>
+    <t>объяснение</t>
   </si>
 </sst>
 </file>
@@ -1193,7 +1193,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7AA31B9-FFFB-4CBC-BB30-C1356C5A3B5F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48181F04-9E86-49E3-A50C-134AB096CA59}">
   <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1568,7 +1568,7 @@
         <v>35</v>
       </c>
       <c r="C34">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
